--- a/experiments/20250716_SOO/iteration_2/raw_data/raw_absorbance_i2.xlsx
+++ b/experiments/20250716_SOO/iteration_2/raw_data/raw_absorbance_i2.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Surfactant\0711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EB79BF9-5FF0-49BB-97AE-F5055DF09C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD736DDE-0A00-4DF4-86A9-FBD16CDD8FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="9528" windowHeight="10356"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="9528" windowHeight="10356"/>
   </bookViews>
   <sheets>
     <sheet name="Plate 1 - Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MethodPointer1">1488579456</definedName>
+    <definedName name="MethodPointer1">1773412528</definedName>
     <definedName name="MethodPointer2">396</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +46,7 @@
     <t>Experiment File Path:</t>
   </si>
   <si>
-    <t>D:\Surfactant\0711\ot-2.xpt</t>
+    <t>D:\Surfactant\0711\ot-1.xpt</t>
   </si>
   <si>
     <t>Protocol File Path:</t>
@@ -97,7 +97,7 @@
     <t>Absorbance Endpoint</t>
   </si>
   <si>
-    <t>A1..B12</t>
+    <t>G1..H12</t>
   </si>
   <si>
     <t>Wavelengths:  600</t>
@@ -172,7 +172,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -187,61 +187,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE8F3FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6FA9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CC5E5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DBCE0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3385C2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABCEEA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E0F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF247CBD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD8E9F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC9E0F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF247CBD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60A0D1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF428EC7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CC5E5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DBCE0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABCEEA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF5197CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -273,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -292,15 +298,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -320,6 +326,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -350,39 +359,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -434,7 +443,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -545,6 +554,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -553,13 +569,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -624,28 +633,13 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
@@ -700,7 +694,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0.63031249999999994</v>
+        <v>0.55170138888888887</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -780,7 +774,7 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>23.7</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -826,43 +820,19 @@
       <c r="B25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="D25" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="E25" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="F25" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="G25" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="H25" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="I25" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="J25" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="K25" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="L25" s="8">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="M25" s="8">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="N25" s="9">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="O25" s="10">
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="8">
         <v>600</v>
       </c>
     </row>
@@ -870,43 +840,19 @@
       <c r="B26" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="D26" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="F26" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="G26" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="H26" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="I26" s="11">
-        <v>8.6999999999999994E-2</v>
-      </c>
-      <c r="J26" s="12">
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="K26" s="13">
-        <v>7.8E-2</v>
-      </c>
-      <c r="L26" s="14">
-        <v>5.8000000000000003E-2</v>
-      </c>
-      <c r="M26" s="15">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="N26" s="16">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="O26" s="10">
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="8">
         <v>600</v>
       </c>
     </row>
@@ -914,19 +860,19 @@
       <c r="B27" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="10">
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="8">
         <v>600</v>
       </c>
     </row>
@@ -934,19 +880,19 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="10">
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="8">
         <v>600</v>
       </c>
     </row>
@@ -954,19 +900,19 @@
       <c r="B29" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="10">
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="8">
         <v>600</v>
       </c>
     </row>
@@ -974,19 +920,19 @@
       <c r="B30" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="10">
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="8">
         <v>600</v>
       </c>
     </row>
@@ -994,19 +940,43 @@
       <c r="B31" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="10">
+      <c r="C31" s="9">
+        <v>0.04</v>
+      </c>
+      <c r="D31" s="9">
+        <v>3.9E-2</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.04</v>
+      </c>
+      <c r="F31" s="9">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="G31" s="9">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="H31" s="9">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="I31" s="10">
+        <v>1.464</v>
+      </c>
+      <c r="J31" s="11">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="K31" s="12">
+        <v>1.19</v>
+      </c>
+      <c r="L31" s="13">
+        <v>2.238</v>
+      </c>
+      <c r="M31" s="13">
+        <v>2.2440000000000002</v>
+      </c>
+      <c r="N31" s="13">
+        <v>2.1909999999999998</v>
+      </c>
+      <c r="O31" s="8">
         <v>600</v>
       </c>
     </row>
@@ -1014,19 +984,43 @@
       <c r="B32" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="10">
+      <c r="C32" s="14">
+        <v>0.89800000000000002</v>
+      </c>
+      <c r="D32" s="15">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="E32" s="11">
+        <v>0.97</v>
+      </c>
+      <c r="F32" s="16">
+        <v>2.4540000000000002</v>
+      </c>
+      <c r="G32" s="13">
+        <v>2.1859999999999999</v>
+      </c>
+      <c r="H32" s="16">
+        <v>2.3660000000000001</v>
+      </c>
+      <c r="I32" s="12">
+        <v>1.1040000000000001</v>
+      </c>
+      <c r="J32" s="11">
+        <v>0.93</v>
+      </c>
+      <c r="K32" s="11">
+        <v>1.004</v>
+      </c>
+      <c r="L32" s="17">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="M32" s="13">
+        <v>2.254</v>
+      </c>
+      <c r="N32" s="18">
+        <v>1.9</v>
+      </c>
+      <c r="O32" s="8">
         <v>600</v>
       </c>
     </row>
